--- a/Sprint1/Doc/ประวัติการใช้ AI.xlsx
+++ b/Sprint1/Doc/ประวัติการใช้ AI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pitim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C729D5E-BB36-4402-96A0-C2B39EA23582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D723854-EE90-4D57-88EF-8E1A4F0830C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>นายณัฐภัทร วรจินดา</t>
   </si>
@@ -95,6 +95,15 @@
   <si>
     <t>ใช้ในการช่วยแนะนำการแก้ไขปัญหา notification</t>
   </si>
+  <si>
+    <t>นายปิติ มูลเทพพิชัย</t>
+  </si>
+  <si>
+    <t>Claude opu&amp;ChatGPT</t>
+  </si>
+  <si>
+    <t>นำมาใช้ในการช่วยรันAPI Add Robot Framework tests &amp; docs for Pickup Notification</t>
+  </si>
 </sst>
 </file>
 
@@ -111,12 +120,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -644,10 +655,16 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+    <row r="9" spans="1:26" ht="51.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
